--- a/human_resources_surveys/046_self_assessment_form--human_resources_surveys.xlsx
+++ b/human_resources_surveys/046_self_assessment_form--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3511,12 +3511,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3613,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3630,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3647,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3681,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -3885,12 +3885,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3919,12 +3919,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3936,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4072,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4123,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -4276,12 +4276,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4293,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4310,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4446,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4463,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4531,12 +4531,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4633,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -4650,12 +4650,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -4735,12 +4735,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4803,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>{'option_0':_'option_0'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{'option_0': 'Option 0'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4820,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>{'option_1':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{'option_1': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>{'option_2':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>{'option_2': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>{'option_3':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>{'option_3': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>{'option_4':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>{'option_4': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -4888,12 +4888,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>{'option_5':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>{'option_5': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>{'option_6':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>{'option_6': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>{'option_7':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>{'option_7': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>{'option_8':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>{'option_8': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
